--- a/Entrega_1/Escrito/Calculos_Excel/cotas.xlsx
+++ b/Entrega_1/Escrito/Calculos_Excel/cotas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elkin\Desktop\Vias\DGV\Entrega_1\Word\Calculos_Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elkin\Desktop\Vias\DGV\Entrega_1\Escrito\Calculos_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7989A0FA-4B7F-4916-BAD8-541F644019D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D5EC73D-2146-42B2-8686-743E031A1F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{3D93F483-E2DE-43E5-9842-92E4A9D352A8}"/>
   </bookViews>
@@ -465,7 +465,7 @@
         <v>1190952.6510000001</v>
       </c>
       <c r="F3" s="1">
-        <v>1712.0663999999999</v>
+        <v>1710.0663999999999</v>
       </c>
     </row>
     <row r="4" spans="3:6" x14ac:dyDescent="0.25">
